--- a/docs/testing/test-script.xlsx
+++ b/docs/testing/test-script.xlsx
@@ -15,7 +15,7 @@
     <sheet name="สรุปผล" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test cases'!$A$1:$L$54</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test cases'!$A$1:$L$64</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -267,12 +267,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="436">
   <si>
     <t xml:space="preserve">OCL Agent · Test script สำหรับทีม (POC นำเข้าข้อมูลเล่มหลักสูตรด้วย AI)</t>
   </si>
   <si>
-    <t xml:space="preserve">เวอร์ชันระบบ: commit หลัง auth (22 ต.ค. 2569) · server http://100.104.172.122:8100/import (ต้องอยู่ใน Tailscale) · dev บน Mac http://localhost:3000/import</t>
+    <t xml:space="preserve">เวอร์ชันระบบ: commit หลัง workflow คู่มือหลักสูตร (22 ต.ค. 2569) · server http://100.104.172.122:8100/import (ต้องอยู่ใน Tailscale) · dev บน Mac http://localhost:3000/import</t>
   </si>
   <si>
     <t xml:space="preserve">ก่อนเริ่ม</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">ลำดับที่แนะนำ</t>
   </si>
   <si>
-    <t xml:space="preserve">J auth (login/บทบาท) → A ตรวจระบบ → B อัปโหลด → C สกัด (ไม่ใช้ AI) → D หน้าตรวจทุกส่วน → E ปิดงาน → F สกัดด้วย AI 1 เล่ม → G server (PM หรือคนที่เข้า server ได้) → H golden (Admin ตรวจกับเล่ม) → I API</t>
+    <t xml:space="preserve">J auth (login/บทบาท) → A ตรวจระบบ → B อัปโหลด → C สกัด (ไม่ใช้ AI) → D หน้าตรวจทุกส่วน → E ปิดงาน → F สกัดด้วย AI 1 เล่ม → G server (PM หรือคนที่เข้า server ได้) → H golden (Admin ตรวจกับเล่ม) → I API → K workflow คู่มือหลักสูตร (ต้องมีบัญชี admin/central + faculty)</t>
   </si>
   <si>
     <t xml:space="preserve">สีที่ใช้</t>
@@ -1185,6 +1185,141 @@
   </si>
   <si>
     <t xml:space="preserve">ได้ [] ไม่ error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/curricula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เมนู 'คู่มือหลักสูตรตาม TOR' แสดงรายการ + ตัวนับ 4 สถานะ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login admin → เมนูซ้าย คู่มือหลักสูตร → คู่มือหลักสูตรตาม TOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">งานที่กด 'บันทึกเข้าระบบ' แล้ว</t>
+  </si>
+  <si>
+    <t xml:space="preserve">การ์ด 4 ใบ: ร่างนำเข้าหลักสูตร / คณะตรวจสอบ / ตรวจสอบสำเร็จ / เผยแพร่แล้ว ตัวเลขรวมเท่าจำนวนแถวในตาราง · คลิกการ์ดเพื่อกรองได้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">หน้า 'บันทึกแล้ว' มีปุ่มเปิดคู่มือหลักสูตร</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ปิดงานใดงานหนึ่ง (E) → หน้า done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">กล่องเขียว 'บันทึกเป็นคู่มือหลักสูตรสถานะ 1. ร่างนำเข้าหลักสูตร' + ปุ่ม 'เปิดคู่มือหลักสูตร' พาไป /curricula/&lt;n&gt; ของงานนั้น</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/curricula/&lt;n&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ส่งให้คณะตรวจสอบ (admin/central/curator)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เปิดคู่มือสถานะร่าง → พิมพ์หมายเหตุ → กด 'ส่งให้คณะตรวจสอบ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สถานะเป็น 'คณะตรวจสอบ' ขั้นตอน 1 ติ๊ก ✓ · แสดง 'กำหนดตรวจภายใน &lt;วันที่&gt;' = วันนี้ + 5 วันทำการ (ข้ามเสาร์-อาทิตย์) · ประวัติมีแถว 'ส่งให้คณะตรวจสอบ' พร้อมอีเมลผู้กดและหมายเหตุ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faculty: ติ๊กหมวด 3 และ 4 แล้วกด 'ตรวจสอบสำเร็จ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ออกจากระบบ → login faculty → เปิดคู่มือเดิม → ติ๊ก 'หมวด 3' → ติ๊ก 'หมวด 4' → กด 'ตรวจสอบสำเร็จ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ก่อนติ๊กครบ ปุ่ม 'ตรวจสอบสำเร็จ' กดไม่ได้ · ติ๊กแต่ละครั้งบันทึกทันที (รีเฟรชแล้วยังติ๊กอยู่) · หลังกด สถานะ 'ตรวจสอบสำเร็จ' + กล่อง 'ข้อมูลถูกล็อก…' · ประวัติมี 2 แถว 'ติ๊กตรวจสอบหมวด' + 1 แถว 'ตรวจสอบสำเร็จ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faculty แก้ได้เฉพาะหมวด 3–4 ระหว่างคณะตรวจสอบ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ทำอีกคู่มือ: admin ส่งให้คณะตรวจสอบ → login faculty → เปิด 'ข้อมูลที่นำเข้า' → แก้ PLO แล้วบันทึกร่าง → แก้รายวิชาแล้วบันทึกร่าง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">หน้าตรวจมีกล่องเหลือง 'อยู่ระหว่างคณะตรวจสอบ · แก้ได้เฉพาะหมวด 3–4' · PLO/KSEC/Mapping บันทึกได้ · รายวิชา/หมวดอื่นถูกปฏิเสธ (ข้อความ 'บัญชีนี้ไม่มีสิทธิ์แก้ไขส่วนนี้')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faculty ส่งคืนส่วนกลางพร้อมเหตุผล</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login faculty → คู่มือสถานะคณะตรวจสอบ → พิมพ์หมายเหตุ → กด 'ส่งคืนส่วนกลาง'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไม่พิมพ์หมายเหตุปุ่มกดไม่ได้ · หลังกด สถานะกลับเป็น 'ร่างนำเข้าหลักสูตร' กำหนดตรวจหาย · ส่งใหม่แล้วติ๊กหมวดเดิมถูกล้าง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/import/&lt;id&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">หลังตรวจสอบสำเร็จ ข้อมูลถูกล็อกทุกบทบาท</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login admin → เปิด 'ข้อมูลที่นำเข้า' ของคู่มือที่ตรวจสอบสำเร็จ → แก้ค่าใดก็ได้ → บันทึกร่าง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">กล่องฟ้า 'คู่มือหลักสูตรนี้ ตรวจสอบสำเร็จ แล้ว ข้อมูลถูกล็อก' · บันทึกถูกปฏิเสธ ข้อความ 'ถูกล็อก แก้ได้ผ่าน สมอ.08 เท่านั้น'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เปิด/ปิดการเผยแพร่ (admin/central เท่านั้น)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login admin → คู่มือสถานะตรวจสอบสำเร็จ → 'เปิดเผยแพร่' → 'ปิดการเผยแพร่'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">สถานะ 'เผยแพร่แล้ว' แล้วกลับเป็น 'ตรวจสอบสำเร็จ' · login faculty ไม่เห็นปุ่มเผยแพร่ (ข้อความ 'เปิด/ปิดการเผยแพร่โดยผู้ดูแลส่วนกลาง')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faculty กด 'ส่งให้คณะตรวจสอบ' ไม่ได้ · admin ข้ามขั้นไม่ได้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login faculty → คู่มือสถานะร่าง · PM: เรียก API POST /api/curricula/&lt;n&gt;/transition action=publish กับคู่มือสถานะร่าง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faculty: ปุ่มส่งตรวจเป็นสีเทา + ข้อความ 'เฉพาะผู้ดูแลส่วนกลาง/ผู้ตรวจสอบระดับหลักสูตร' · API ตอบ 409 'ทำ เปิดเผยแพร่ ได้เฉพาะเมื่อสถานะเป็น ตรวจสอบสำเร็จ'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เวลาในประวัติเป็นเวลาไทย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ดูคอลัมน์ 'วันเวลา' ของประวัติการดำเนินการหลังทำขั้นใดขั้นหนึ่ง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ตรงกับนาฬิกาเครื่อง (เขตเวลา Asia/Bangkok) ไม่ช้า 7 ชั่วโมง</t>
   </si>
   <si>
     <t xml:space="preserve">เล่ม</t>
@@ -2151,7 +2286,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -3700,10 +3835,290 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
     </row>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L54"/>
+  <autoFilter ref="A1:L64"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I54" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I64" type="list">
       <formula1>"ผ่าน,ไม่ผ่าน,ข้าม,บล็อก"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3744,31 +4159,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>306</v>
+        <v>351</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>312</v>
+        <v>357</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>147</v>
@@ -3777,27 +4192,27 @@
         <v>152</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>318</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>320</v>
+        <v>365</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>78</v>
@@ -3806,10 +4221,10 @@
         <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>322</v>
+        <v>367</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>5</v>
@@ -3827,27 +4242,27 @@
         <v>57</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>323</v>
+        <v>368</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>326</v>
+        <v>371</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>186</v>
@@ -3856,10 +4271,10 @@
         <v>33</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>4</v>
@@ -3877,27 +4292,27 @@
         <v>78</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>332</v>
+        <v>377</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>335</v>
+        <v>380</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>75</v>
@@ -3906,10 +4321,10 @@
         <v>34</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>339</v>
+        <v>384</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>340</v>
+        <v>385</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>3</v>
@@ -3927,27 +4342,27 @@
         <v>24</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>343</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>344</v>
+        <v>389</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>221</v>
@@ -3956,10 +4371,10 @@
         <v>33</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>346</v>
+        <v>391</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>347</v>
+        <v>392</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>6</v>
@@ -3977,27 +4392,27 @@
         <v>90</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>348</v>
+        <v>393</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>349</v>
+        <v>394</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>350</v>
+        <v>395</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>351</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>352</v>
+        <v>397</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>353</v>
+        <v>398</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>56</v>
@@ -4006,13 +4421,13 @@
         <v>33</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>339</v>
+        <v>384</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>354</v>
+        <v>399</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>38</v>
@@ -4027,24 +4442,24 @@
         <v>17</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>356</v>
+        <v>401</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>359</v>
+        <v>404</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -4080,31 +4495,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>362</v>
+        <v>407</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>364</v>
+        <v>409</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>366</v>
+        <v>411</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>367</v>
+        <v>412</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>369</v>
+        <v>414</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>26</v>
@@ -4113,33 +4528,33 @@
         <v>24</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>371</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>372</v>
+        <v>417</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>131</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>373</v>
+        <v>418</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>374</v>
+        <v>419</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>375</v>
+        <v>420</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>376</v>
+        <v>421</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>37</v>
@@ -4148,7 +4563,7 @@
         <v>38</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>379</v>
+        <v>424</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>33</v>
@@ -4741,7 +5156,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -4755,7 +5170,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>380</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4763,25 +5178,25 @@
         <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>381</v>
+        <v>426</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>382</v>
+        <v>427</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>383</v>
+        <v>428</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>384</v>
+        <v>429</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>385</v>
+        <v>430</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4789,23 +5204,23 @@
         <v>40</v>
       </c>
       <c r="B4" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A4)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A4)</f>
         <v>3</v>
       </c>
       <c r="C4" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A4,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A4,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D4" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A4,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A4,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E4" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A4,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A4,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F4" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A4,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A4,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G4" s="10" t="n">
@@ -4822,23 +5237,23 @@
         <v>54</v>
       </c>
       <c r="B5" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A5)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A5)</f>
         <v>6</v>
       </c>
       <c r="C5" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A5,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A5,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D5" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A5,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A5,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E5" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A5,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A5,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F5" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A5,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A5,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
@@ -4855,23 +5270,23 @@
         <v>85</v>
       </c>
       <c r="B6" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A6)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A6)</f>
         <v>3</v>
       </c>
       <c r="C6" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A6,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A6,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D6" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A6,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A6,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E6" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A6,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A6,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F6" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A6,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A6,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -4888,23 +5303,23 @@
         <v>102</v>
       </c>
       <c r="B7" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A7)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A7)</f>
         <v>15</v>
       </c>
       <c r="C7" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A7,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A7,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A7,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A7,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E7" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A7,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A7,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F7" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A7,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A7,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -4921,23 +5336,23 @@
         <v>176</v>
       </c>
       <c r="B8" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A8)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A8)</f>
         <v>4</v>
       </c>
       <c r="C8" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A8,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A8,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D8" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A8,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A8,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E8" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A8,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A8,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F8" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A8,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A8,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -4954,23 +5369,23 @@
         <v>196</v>
       </c>
       <c r="B9" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A9)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A9)</f>
         <v>3</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A9,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A9,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D9" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A9,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A9,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E9" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A9,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A9,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F9" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A9,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A9,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -4987,23 +5402,23 @@
         <v>212</v>
       </c>
       <c r="B10" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A10)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A10)</f>
         <v>6</v>
       </c>
       <c r="C10" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A10,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A10,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D10" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A10,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A10,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E10" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A10,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A10,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F10" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A10,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A10,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -5020,23 +5435,23 @@
         <v>242</v>
       </c>
       <c r="B11" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A11)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A11,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A11,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D11" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A11,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A11,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E11" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A11,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A11,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F11" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A11,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A11,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -5053,23 +5468,23 @@
         <v>291</v>
       </c>
       <c r="B12" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A12)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A12)</f>
         <v>3</v>
       </c>
       <c r="C12" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A12,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A12,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D12" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A12,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A12,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E12" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A12,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A12,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F12" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A12,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A12,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -5086,23 +5501,23 @@
         <v>249</v>
       </c>
       <c r="B13" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$54,A13)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A13)</f>
         <v>8</v>
       </c>
       <c r="C13" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A13,'Test cases'!$I$3:$I$54,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A13,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D13" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A13,'Test cases'!$I$3:$I$54,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A13,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E13" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A13,'Test cases'!$I$3:$I$54,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A13,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F13" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$54,A13,'Test cases'!$I$3:$I$54,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A13,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
@@ -5115,59 +5530,92 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="B14" s="12" t="n">
-        <f aca="false">SUM(B4:B13)</f>
-        <v>52</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <f aca="false">SUM(C4:C13)</f>
+      <c r="A14" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="10" t="n">
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A14)</f>
+        <v>10</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A14,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
         <v>0</v>
       </c>
-      <c r="D14" s="12" t="n">
-        <f aca="false">SUM(D4:D13)</f>
+      <c r="D14" s="10" t="n">
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A14,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
-      <c r="E14" s="12" t="n">
-        <f aca="false">SUM(E4:E13)</f>
+      <c r="E14" s="10" t="n">
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A14,'Test cases'!$I$3:$I$64,"ข้าม")</f>
         <v>0</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <f aca="false">SUM(F4:F13)</f>
+      <c r="F14" s="10" t="n">
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A14,'Test cases'!$I$3:$I$64,"บล็อก")</f>
         <v>0</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <f aca="false">SUM(G4:G13)</f>
-        <v>52</v>
-      </c>
-      <c r="H14" s="13" t="str">
+      <c r="G14" s="10" t="n">
+        <f aca="false">B14-C14-D14-E14-F14</f>
+        <v>10</v>
+      </c>
+      <c r="H14" s="11" t="str">
         <f aca="false">IF(C14+D14=0,"-",C14/(C14+D14))</f>
         <v>-</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="B16" s="0" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <f aca="false">SUM(B4:B14)</f>
+        <v>62</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <f aca="false">SUM(C4:C14)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <f aca="false">SUM(D4:D14)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <f aca="false">SUM(E4:E14)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <f aca="false">SUM(F4:F14)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <f aca="false">SUM(G4:G14)</f>
+        <v>62</v>
+      </c>
+      <c r="H15" s="13" t="str">
+        <f aca="false">IF(C15+D15=0,"-",C15/(C15+D15))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="B17" s="0" t="n">
         <f aca="false">COUNTIF('Issue log'!$K$3:$K$42,"เปิด")+COUNTIF('Issue log'!$K$3:$K$42,"กำลังแก้")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>389</v>
-      </c>
-      <c r="B17" s="0" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <f aca="false">COUNTIFS('Issue log'!$C$3:$C$42,"สูง",'Issue log'!$K$3:$K$42,"&lt;&gt;ปิด",'Issue log'!$K$3:$K$42,"&lt;&gt;แก้แล้ว",'Issue log'!$K$3:$K$42,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>390</v>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/docs/testing/test-script.xlsx
+++ b/docs/testing/test-script.xlsx
@@ -15,7 +15,7 @@
     <sheet name="สรุปผล" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test cases'!$A$1:$L$64</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Test cases'!$A$1:$L$68</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -267,12 +267,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="454">
   <si>
     <t xml:space="preserve">OCL Agent · Test script สำหรับทีม (POC นำเข้าข้อมูลเล่มหลักสูตรด้วย AI)</t>
   </si>
   <si>
-    <t xml:space="preserve">เวอร์ชันระบบ: commit หลัง workflow คู่มือหลักสูตร (22 ต.ค. 2569) · server http://100.104.172.122:8100/import (ต้องอยู่ใน Tailscale) · dev บน Mac http://localhost:3000/import</t>
+    <t xml:space="preserve">เวอร์ชันระบบ: commit หลัง OCR หน้าสแกน (22 ต.ค. 2569) · server http://100.104.172.122:8100/import (ต้องอยู่ใน Tailscale) · dev บน Mac http://localhost:3000/import</t>
   </si>
   <si>
     <t xml:space="preserve">ก่อนเริ่ม</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">ลำดับที่แนะนำ</t>
   </si>
   <si>
-    <t xml:space="preserve">J auth (login/บทบาท) → A ตรวจระบบ → B อัปโหลด → C สกัด (ไม่ใช้ AI) → D หน้าตรวจทุกส่วน → E ปิดงาน → F สกัดด้วย AI 1 เล่ม → G server (PM หรือคนที่เข้า server ได้) → H golden (Admin ตรวจกับเล่ม) → I API → K workflow คู่มือหลักสูตร (ต้องมีบัญชี admin/central + faculty)</t>
+    <t xml:space="preserve">J auth (login/บทบาท) → A ตรวจระบบ → B อัปโหลด → C สกัด (ไม่ใช้ AI) → D หน้าตรวจทุกส่วน → E ปิดงาน → F สกัดด้วย AI 1 เล่ม → G server (PM หรือคนที่เข้า server ได้) → H golden (Admin ตรวจกับเล่ม) → I API → K workflow คู่มือหลักสูตร (ต้องมีบัญชี admin/central + faculty) → L OCR หน้าสแกน</t>
   </si>
   <si>
     <t xml:space="preserve">สีที่ใช้</t>
@@ -1320,6 +1320,60 @@
   </si>
   <si>
     <t xml:space="preserve">ตรงกับนาฬิกาเครื่อง (เขตเวลา Asia/Bangkok) ไม่ช้า 7 ชั่วโมง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L OCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF สแกน (ไม่มี text layer) อ่านได้ด้วย OCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ขอไฟล์ 'วท.บ. อาหาร (สแกน 14 หน้า).pdf' จาก PM (สร้างจากเล่มดิจิทัล) → อัปโหลดแบบ 'อ่านด้วยกฎเท่านั้น'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scan-book14.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">งานเสร็จใน ~1 นาที (OCR ~3 วินาที/หน้า) · แผง 'ต้นฉบับ' หน้า 1 แสดงรูปหน้าสแกน + ข้อความที่ OCR ได้ (สะกดเพี้ยนบ้าง เช่น วรรณยุกต์หาย) · หน้า done แสดง 'หน้าสแกน 14 (OCR 14)'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">หมวดจากหน้าสแกนถูกแยกถูก</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เปิดงานเดิม → Preview แบบเล่ม / book.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">มีหัวข้อ 'หมวดที่ 1 …' และ 'หมวดที่ 2 …' จากหน้า 5 และ 11 · บรรทัดสารบัญที่ OCR เพี้ยนไม่กลายเป็นหมวด</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">server มีไฟล์ภาษา OCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เปิด http://100.104.172.122:8100/health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">มี "ocr":"tha+eng" (ถ้าเป็น null = image ไม่มี tessdata แจ้ง PM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ข้อมูลจากหน้าสแกนต้องพึ่ง AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อัปโหลดไฟล์สแกนเดิมด้วย Local AI · Gemma แล้วเทียบส่วนที่ 1 กับรอบ 'กฎเท่านั้น'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">รอบกฎเท่านั้นได้ฟิลด์ว่างเกือบทั้งหมด (OCR สะกดเพี้ยนจน parser จับไม่ได้) · รอบ AI เติมฟิลด์ได้มากขึ้น ค่าที่ได้ต้องตรวจกับรูปหน้าสแกนทุกค่า</t>
   </si>
   <si>
     <t xml:space="preserve">เล่ม</t>
@@ -2286,7 +2340,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -4115,10 +4169,122 @@
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
     </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L64"/>
+  <autoFilter ref="A1:L68"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I64" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I68" type="list">
       <formula1>"ผ่าน,ไม่ผ่าน,ข้าม,บล็อก"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4159,31 +4325,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>137</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>147</v>
@@ -4192,27 +4358,27 @@
         <v>152</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>78</v>
@@ -4221,10 +4387,10 @@
         <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>5</v>
@@ -4242,27 +4408,27 @@
         <v>57</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>186</v>
@@ -4271,10 +4437,10 @@
         <v>33</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>4</v>
@@ -4292,27 +4458,27 @@
         <v>78</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>75</v>
@@ -4321,10 +4487,10 @@
         <v>34</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>3</v>
@@ -4342,27 +4508,27 @@
         <v>24</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>221</v>
@@ -4371,10 +4537,10 @@
         <v>33</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>6</v>
@@ -4392,27 +4558,27 @@
         <v>90</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>56</v>
@@ -4421,13 +4587,13 @@
         <v>33</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>38</v>
@@ -4442,24 +4608,24 @@
         <v>17</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -4495,31 +4661,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>26</v>
@@ -4528,33 +4694,33 @@
         <v>24</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>131</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>37</v>
@@ -4563,7 +4729,7 @@
         <v>38</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>33</v>
@@ -5156,7 +5322,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -5170,7 +5336,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5178,25 +5344,25 @@
         <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5204,23 +5370,23 @@
         <v>40</v>
       </c>
       <c r="B4" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A4)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A4)</f>
         <v>3</v>
       </c>
       <c r="C4" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A4,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A4,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D4" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A4,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A4,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E4" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A4,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A4,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F4" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A4,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A4,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G4" s="10" t="n">
@@ -5237,23 +5403,23 @@
         <v>54</v>
       </c>
       <c r="B5" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A5)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A5)</f>
         <v>6</v>
       </c>
       <c r="C5" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A5,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A5,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D5" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A5,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A5,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E5" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A5,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A5,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F5" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A5,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A5,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G5" s="10" t="n">
@@ -5270,23 +5436,23 @@
         <v>85</v>
       </c>
       <c r="B6" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A6)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A6)</f>
         <v>3</v>
       </c>
       <c r="C6" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A6,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A6,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D6" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A6,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A6,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E6" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A6,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A6,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F6" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A6,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A6,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -5303,23 +5469,23 @@
         <v>102</v>
       </c>
       <c r="B7" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A7)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A7)</f>
         <v>15</v>
       </c>
       <c r="C7" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A7,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A7,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A7,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A7,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E7" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A7,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A7,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F7" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A7,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A7,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -5336,23 +5502,23 @@
         <v>176</v>
       </c>
       <c r="B8" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A8)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A8)</f>
         <v>4</v>
       </c>
       <c r="C8" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A8,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A8,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D8" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A8,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A8,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E8" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A8,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A8,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F8" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A8,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A8,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -5369,23 +5535,23 @@
         <v>196</v>
       </c>
       <c r="B9" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A9)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A9)</f>
         <v>3</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A9,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A9,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D9" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A9,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A9,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E9" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A9,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A9,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F9" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A9,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A9,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -5402,23 +5568,23 @@
         <v>212</v>
       </c>
       <c r="B10" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A10)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A10)</f>
         <v>6</v>
       </c>
       <c r="C10" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A10,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A10,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D10" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A10,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A10,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E10" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A10,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A10,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F10" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A10,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A10,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -5435,23 +5601,23 @@
         <v>242</v>
       </c>
       <c r="B11" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A11)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A11,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A11,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D11" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A11,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A11,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E11" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A11,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A11,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F11" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A11,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A11,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -5468,23 +5634,23 @@
         <v>291</v>
       </c>
       <c r="B12" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A12)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A12)</f>
         <v>3</v>
       </c>
       <c r="C12" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A12,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A12,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D12" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A12,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A12,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E12" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A12,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A12,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F12" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A12,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A12,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -5501,23 +5667,23 @@
         <v>249</v>
       </c>
       <c r="B13" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A13)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A13)</f>
         <v>8</v>
       </c>
       <c r="C13" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A13,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A13,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D13" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A13,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A13,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E13" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A13,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A13,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F13" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A13,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A13,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
@@ -5534,23 +5700,23 @@
         <v>307</v>
       </c>
       <c r="B14" s="10" t="n">
-        <f aca="false">COUNTIF('Test cases'!$B$3:$B$64,A14)</f>
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A14)</f>
         <v>10</v>
       </c>
       <c r="C14" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A14,'Test cases'!$I$3:$I$64,"ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A14,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="D14" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A14,'Test cases'!$I$3:$I$64,"ไม่ผ่าน")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A14,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
       <c r="E14" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A14,'Test cases'!$I$3:$I$64,"ข้าม")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A14,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
       <c r="F14" s="10" t="n">
-        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$64,A14,'Test cases'!$I$3:$I$64,"บล็อก")</f>
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A14,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -5563,59 +5729,92 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="B15" s="12" t="n">
-        <f aca="false">SUM(B4:B14)</f>
-        <v>62</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <f aca="false">SUM(C4:C14)</f>
+      <c r="A15" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B15" s="10" t="n">
+        <f aca="false">COUNTIF('Test cases'!$B$3:$B$68,A15)</f>
+        <v>4</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A15,'Test cases'!$I$3:$I$68,"ผ่าน")</f>
         <v>0</v>
       </c>
-      <c r="D15" s="12" t="n">
-        <f aca="false">SUM(D4:D14)</f>
+      <c r="D15" s="10" t="n">
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A15,'Test cases'!$I$3:$I$68,"ไม่ผ่าน")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <f aca="false">SUM(E4:E14)</f>
+      <c r="E15" s="10" t="n">
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A15,'Test cases'!$I$3:$I$68,"ข้าม")</f>
         <v>0</v>
       </c>
-      <c r="F15" s="12" t="n">
-        <f aca="false">SUM(F4:F14)</f>
+      <c r="F15" s="10" t="n">
+        <f aca="false">COUNTIFS('Test cases'!$B$3:$B$68,A15,'Test cases'!$I$3:$I$68,"บล็อก")</f>
         <v>0</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <f aca="false">SUM(G4:G14)</f>
-        <v>62</v>
-      </c>
-      <c r="H15" s="13" t="str">
+      <c r="G15" s="10" t="n">
+        <f aca="false">B15-C15-D15-E15-F15</f>
+        <v>4</v>
+      </c>
+      <c r="H15" s="11" t="str">
         <f aca="false">IF(C15+D15=0,"-",C15/(C15+D15))</f>
         <v>-</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="B17" s="0" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <f aca="false">SUM(B4:B15)</f>
+        <v>66</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <f aca="false">SUM(C4:C15)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <f aca="false">SUM(D4:D15)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <f aca="false">SUM(E4:E15)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <f aca="false">SUM(F4:F15)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <f aca="false">SUM(G4:G15)</f>
+        <v>66</v>
+      </c>
+      <c r="H16" s="13" t="str">
+        <f aca="false">IF(C16+D16=0,"-",C16/(C16+D16))</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <f aca="false">COUNTIF('Issue log'!$K$3:$K$42,"เปิด")+COUNTIF('Issue log'!$K$3:$K$42,"กำลังแก้")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="B18" s="0" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="B19" s="0" t="n">
         <f aca="false">COUNTIFS('Issue log'!$C$3:$C$42,"สูง",'Issue log'!$K$3:$K$42,"&lt;&gt;ปิด",'Issue log'!$K$3:$K$42,"&lt;&gt;แก้แล้ว",'Issue log'!$K$3:$K$42,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>435</v>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
